--- a/disabled products/Gen 2.5 12-Door Beer.xlsx
+++ b/disabled products/Gen 2.5 12-Door Beer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jenn/Documents/QuikTrip/2024 Reset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374EB9C2-F29B-174A-AAF6-0D7F1B47DA3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D625A0E-79EC-6241-A627-F4A596A06786}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="12760" windowHeight="14400" xr2:uid="{E26AF1C9-6286-E04F-A149-A99C470D1576}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="610">
   <si>
     <t>068274463334</t>
   </si>
@@ -468,9 +468,6 @@
     <t>684746400074</t>
   </si>
   <si>
-    <t>634985245950</t>
-  </si>
-  <si>
     <t>635985132196</t>
   </si>
   <si>
@@ -579,9 +576,6 @@
     <t>Clubtails Sex On The Beach 16oz</t>
   </si>
   <si>
-    <t>Mike's Harder Seasonal 16oz</t>
-  </si>
-  <si>
     <t>Mike's Harder Strawberry Lemonade 16oz</t>
   </si>
   <si>
@@ -735,9 +729,6 @@
     <t>018200200786</t>
   </si>
   <si>
-    <t>018200200779</t>
-  </si>
-  <si>
     <t>Four Peaks Bad Bird Juice 19.2oz</t>
   </si>
   <si>
@@ -780,9 +771,6 @@
     <t>Natty Daddy 12oz Can 15pk</t>
   </si>
   <si>
-    <t>Natural Light 12oz Can 15pk</t>
-  </si>
-  <si>
     <t>034100003234</t>
   </si>
   <si>
@@ -1332,18 +1320,9 @@
     <t>Buzzballz Chocolate 187mL</t>
   </si>
   <si>
-    <t>857641002333</t>
-  </si>
-  <si>
-    <t>Buzzballz Lotta Colada 187mL</t>
-  </si>
-  <si>
     <t>857641002149</t>
   </si>
   <si>
-    <t>Buzzballz Limearita 187mL</t>
-  </si>
-  <si>
     <t>857641002654</t>
   </si>
   <si>
@@ -1849,6 +1828,33 @@
   </si>
   <si>
     <t>Happy Thursday Strawberry 24oz</t>
+  </si>
+  <si>
+    <t>Buzzballz Limarita 187mL</t>
+  </si>
+  <si>
+    <t>857674007985</t>
+  </si>
+  <si>
+    <t>Buzzballz Berry Cherry Lemonade 187mL</t>
+  </si>
+  <si>
+    <t>182136000120</t>
+  </si>
+  <si>
+    <t>Aquahydrate Gal</t>
+  </si>
+  <si>
+    <t>635985100171</t>
+  </si>
+  <si>
+    <t>Mike's Harder GreenApple 16oz</t>
+  </si>
+  <si>
+    <t>018200152467</t>
+  </si>
+  <si>
+    <t>Natural Light 12oz Can 12pk</t>
   </si>
 </sst>
 </file>
@@ -2210,7 +2216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{803BA958-B48A-ED4D-9B38-59B159FBE8C1}">
-  <dimension ref="A1:C304"/>
+  <dimension ref="A1:C305"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -2223,10 +2229,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2234,10 +2240,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2245,10 +2251,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2278,10 +2284,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2289,10 +2295,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2322,10 +2328,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2333,10 +2339,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2344,10 +2350,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2355,10 +2361,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2366,10 +2372,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2377,10 +2383,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C15" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2388,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C16" t="s">
-        <v>436</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2399,10 +2405,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>437</v>
+        <v>602</v>
       </c>
       <c r="C17" t="s">
-        <v>438</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2410,32 +2416,32 @@
         <v>1</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C18" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>442</v>
+        <v>604</v>
       </c>
       <c r="C20" t="s">
-        <v>443</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2443,10 +2449,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
+        <v>435</v>
       </c>
       <c r="C21" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2454,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2465,10 +2471,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2476,10 +2482,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>447</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2487,10 +2493,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C25" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2498,10 +2504,10 @@
         <v>1</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>118</v>
+        <v>442</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2509,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2520,10 +2526,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2531,10 +2537,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2542,10 +2548,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -2553,10 +2559,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2564,10 +2570,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2575,10 +2581,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>451</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>452</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2586,10 +2592,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>144</v>
+        <v>444</v>
       </c>
       <c r="C34" t="s">
-        <v>181</v>
+        <v>445</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2597,10 +2603,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -2608,10 +2614,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>148</v>
+        <v>606</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>607</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -2619,43 +2625,43 @@
         <v>1</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C37" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>269</v>
+        <v>149</v>
       </c>
       <c r="C39" t="s">
-        <v>301</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C40" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -2663,10 +2669,10 @@
         <v>2</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C41" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -2674,10 +2680,10 @@
         <v>2</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C42" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -2685,21 +2691,21 @@
         <v>2</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C43" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>453</v>
+        <v>269</v>
       </c>
       <c r="C44" t="s">
-        <v>454</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -2707,10 +2713,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>606</v>
+        <v>446</v>
       </c>
       <c r="C45" t="s">
-        <v>607</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -2718,10 +2724,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>455</v>
+        <v>599</v>
       </c>
       <c r="C46" t="s">
-        <v>456</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -2729,10 +2735,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C47" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -2740,10 +2746,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>221</v>
+        <v>451</v>
       </c>
       <c r="C48" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -2751,10 +2757,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C49" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -2762,10 +2768,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="C50" t="s">
-        <v>299</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -2773,32 +2779,32 @@
         <v>1</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C51" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C52" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C53" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -2806,21 +2812,21 @@
         <v>1</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C54" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -2828,32 +2834,32 @@
         <v>2</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C56" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C57" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>252</v>
       </c>
       <c r="C58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -2861,10 +2867,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C59" t="s">
-        <v>462</v>
+        <v>283</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -2872,10 +2878,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>463</v>
+        <v>249</v>
       </c>
       <c r="C60" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -2883,10 +2889,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C61" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -2894,10 +2900,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C62" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -2905,10 +2911,10 @@
         <v>1</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="C63" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -2916,10 +2922,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="C64" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -2927,10 +2933,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C65" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -2938,10 +2944,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="C66" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -2949,10 +2955,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="C67" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -2960,10 +2966,10 @@
         <v>1</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C68" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -2971,10 +2977,10 @@
         <v>1</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C69" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -2982,10 +2988,10 @@
         <v>1</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>254</v>
+        <v>474</v>
       </c>
       <c r="C70" t="s">
-        <v>288</v>
+        <v>475</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -2993,10 +2999,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C71" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -3004,10 +3010,10 @@
         <v>1</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
-        <v>483</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -3015,10 +3021,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C73" t="s">
-        <v>297</v>
+        <v>476</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -3026,10 +3032,10 @@
         <v>1</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C74" t="s">
-        <v>457</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -3037,10 +3043,10 @@
         <v>1</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>484</v>
+        <v>261</v>
       </c>
       <c r="C75" t="s">
-        <v>485</v>
+        <v>450</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -3048,10 +3054,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>260</v>
+        <v>477</v>
       </c>
       <c r="C76" t="s">
-        <v>294</v>
+        <v>478</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -3059,10 +3065,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>486</v>
+        <v>256</v>
       </c>
       <c r="C77" t="s">
-        <v>487</v>
+        <v>290</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -3070,10 +3076,10 @@
         <v>1</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C78" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -3081,10 +3087,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>261</v>
+        <v>481</v>
       </c>
       <c r="C79" t="s">
-        <v>295</v>
+        <v>482</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -3092,10 +3098,10 @@
         <v>1</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>490</v>
+        <v>257</v>
       </c>
       <c r="C80" t="s">
-        <v>491</v>
+        <v>291</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -3103,10 +3109,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="C81" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -3114,10 +3120,10 @@
         <v>1</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C82" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -3125,10 +3131,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="C83" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -3136,10 +3142,10 @@
         <v>1</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C84" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -3147,10 +3153,10 @@
         <v>1</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>163</v>
+        <v>491</v>
       </c>
       <c r="C85" t="s">
-        <v>200</v>
+        <v>492</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -3158,10 +3164,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C86" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -3169,10 +3175,10 @@
         <v>1</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>500</v>
+        <v>163</v>
       </c>
       <c r="C87" t="s">
-        <v>501</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -3180,10 +3186,10 @@
         <v>1</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C88" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -3191,10 +3197,10 @@
         <v>1</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C89" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -3202,10 +3208,10 @@
         <v>1</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C90" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -3213,10 +3219,10 @@
         <v>1</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C91" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -3224,32 +3230,32 @@
         <v>1</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>166</v>
+        <v>501</v>
       </c>
       <c r="C92" t="s">
-        <v>203</v>
+        <v>502</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C93" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>510</v>
+        <v>164</v>
       </c>
       <c r="C94" t="s">
-        <v>511</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -3257,32 +3263,32 @@
         <v>1</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C95" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>160</v>
+        <v>505</v>
       </c>
       <c r="C96" t="s">
-        <v>197</v>
+        <v>506</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C97" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -3290,10 +3296,10 @@
         <v>1</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>219</v>
+        <v>152</v>
       </c>
       <c r="C98" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -3301,10 +3307,10 @@
         <v>1</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="C99" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -3312,10 +3318,10 @@
         <v>1</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>514</v>
+        <v>155</v>
       </c>
       <c r="C100" t="s">
-        <v>515</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -3323,10 +3329,10 @@
         <v>1</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C101" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -3334,10 +3340,10 @@
         <v>1</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>157</v>
+        <v>509</v>
       </c>
       <c r="C102" t="s">
-        <v>194</v>
+        <v>510</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -3345,7 +3351,7 @@
         <v>1</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C103" t="s">
         <v>192</v>
@@ -3356,10 +3362,10 @@
         <v>1</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -3367,10 +3373,10 @@
         <v>1</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C105" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -3378,10 +3384,10 @@
         <v>1</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C106" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -3389,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C107" t="s">
         <v>189</v>
@@ -3403,7 +3409,7 @@
         <v>151</v>
       </c>
       <c r="C108" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -3411,10 +3417,10 @@
         <v>1</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="C109" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -3422,54 +3428,54 @@
         <v>1</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C110" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C111" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C112" t="s">
-        <v>411</v>
+        <v>130</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C113" t="s">
-        <v>126</v>
+        <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C114" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -3477,21 +3483,21 @@
         <v>3</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>518</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>519</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -3499,10 +3505,10 @@
         <v>1</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C117" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -3510,32 +3516,32 @@
         <v>1</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>158</v>
+        <v>513</v>
       </c>
       <c r="C118" t="s">
-        <v>195</v>
+        <v>514</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="C119" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C120" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -3543,54 +3549,54 @@
         <v>1</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>522</v>
+        <v>112</v>
       </c>
       <c r="C121" t="s">
-        <v>523</v>
+        <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
       <c r="C122" t="s">
-        <v>127</v>
+        <v>516</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="C123" t="s">
-        <v>196</v>
+        <v>127</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="C124" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C125" t="s">
-        <v>218</v>
+        <v>125</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -3598,10 +3604,10 @@
         <v>1</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>524</v>
+        <v>98</v>
       </c>
       <c r="C126" t="s">
-        <v>525</v>
+        <v>216</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -3609,21 +3615,21 @@
         <v>1</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>99</v>
+        <v>517</v>
       </c>
       <c r="C127" t="s">
-        <v>123</v>
+        <v>518</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C128" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -3631,21 +3637,21 @@
         <v>2</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C129" t="s">
-        <v>217</v>
+        <v>124</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C130" t="s">
-        <v>526</v>
+        <v>215</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -3653,32 +3659,32 @@
         <v>1</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C131" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>225</v>
+        <v>95</v>
       </c>
       <c r="C132" t="s">
-        <v>240</v>
+        <v>520</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C133" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -3689,40 +3695,40 @@
         <v>222</v>
       </c>
       <c r="C134" t="s">
-        <v>528</v>
+        <v>236</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C135" t="s">
-        <v>238</v>
+        <v>521</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C136" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C137" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -3730,10 +3736,10 @@
         <v>9</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C138" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -3741,21 +3747,21 @@
         <v>9</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C139" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C140" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -3763,54 +3769,54 @@
         <v>2</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C141" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C142" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C143" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="C144" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C145" t="s">
-        <v>529</v>
+        <v>204</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -3818,21 +3824,21 @@
         <v>2</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C146" t="s">
-        <v>205</v>
+        <v>522</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>168</v>
       </c>
       <c r="C147" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -3840,18 +3846,18 @@
         <v>1</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C148" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C149" t="s">
         <v>207</v>
@@ -3862,21 +3868,21 @@
         <v>2</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C150" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>530</v>
+        <v>171</v>
       </c>
       <c r="C151" t="s">
-        <v>531</v>
+        <v>206</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -3884,10 +3890,10 @@
         <v>1</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>175</v>
+        <v>523</v>
       </c>
       <c r="C152" t="s">
-        <v>211</v>
+        <v>524</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -3898,7 +3904,7 @@
         <v>174</v>
       </c>
       <c r="C153" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -3906,10 +3912,10 @@
         <v>1</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C154" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -3920,7 +3926,7 @@
         <v>176</v>
       </c>
       <c r="C155" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -3928,87 +3934,87 @@
         <v>1</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>532</v>
+        <v>175</v>
       </c>
       <c r="C156" t="s">
-        <v>533</v>
+        <v>210</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="C157" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C158" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="C159" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="C160" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="C161" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C162" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>178</v>
+        <v>537</v>
       </c>
       <c r="C163" t="s">
-        <v>214</v>
+        <v>538</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -4016,10 +4022,10 @@
         <v>1</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="C164" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -4027,10 +4033,10 @@
         <v>1</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>344</v>
+        <v>232</v>
       </c>
       <c r="C165" t="s">
-        <v>358</v>
+        <v>246</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -4038,10 +4044,10 @@
         <v>1</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>179</v>
+        <v>340</v>
       </c>
       <c r="C166" t="s">
-        <v>215</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
@@ -4049,10 +4055,10 @@
         <v>1</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>546</v>
+        <v>178</v>
       </c>
       <c r="C167" t="s">
-        <v>547</v>
+        <v>213</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
@@ -4060,43 +4066,43 @@
         <v>1</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>235</v>
+        <v>539</v>
       </c>
       <c r="C168" t="s">
-        <v>250</v>
+        <v>540</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C169" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>180</v>
+        <v>608</v>
       </c>
       <c r="C170" t="s">
-        <v>216</v>
+        <v>609</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>319</v>
+        <v>179</v>
       </c>
       <c r="C171" t="s">
-        <v>331</v>
+        <v>214</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
@@ -4104,21 +4110,21 @@
         <v>2</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C172" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C173" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
@@ -4126,21 +4132,21 @@
         <v>1</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C174" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C175" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -4148,32 +4154,32 @@
         <v>2</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C176" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C177" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C178" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
@@ -4181,10 +4187,10 @@
         <v>1</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C179" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
@@ -4192,10 +4198,10 @@
         <v>1</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="C180" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
@@ -4203,32 +4209,32 @@
         <v>1</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="C181" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C182" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C183" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
@@ -4236,10 +4242,10 @@
         <v>1</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>548</v>
+        <v>326</v>
       </c>
       <c r="C184" t="s">
-        <v>549</v>
+        <v>338</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -4247,32 +4253,32 @@
         <v>1</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>351</v>
+        <v>541</v>
       </c>
       <c r="C185" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="C186" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C187" t="s">
-        <v>357</v>
+        <v>544</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -4280,43 +4286,43 @@
         <v>1</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="C188" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="C189" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190">
-        <v>1</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C190" s="3" t="s">
-        <v>401</v>
+        <v>2</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C190" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191">
-        <v>2</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C191" t="s">
-        <v>366</v>
+        <v>1</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
@@ -4324,76 +4330,76 @@
         <v>2</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="C192" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C193" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C194" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="C195" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C196" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C197" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C198" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -4401,32 +4407,32 @@
         <v>1</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C199" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="C200" t="s">
-        <v>399</v>
+        <v>355</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>552</v>
+        <v>382</v>
       </c>
       <c r="C201" t="s">
-        <v>553</v>
+        <v>395</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
@@ -4434,10 +4440,10 @@
         <v>1</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>393</v>
+        <v>545</v>
       </c>
       <c r="C202" t="s">
-        <v>405</v>
+        <v>546</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
@@ -4445,10 +4451,10 @@
         <v>1</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>346</v>
+        <v>389</v>
       </c>
       <c r="C203" t="s">
-        <v>360</v>
+        <v>401</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
@@ -4456,10 +4462,10 @@
         <v>1</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C204" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
@@ -4467,10 +4473,10 @@
         <v>1</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>387</v>
+        <v>345</v>
       </c>
       <c r="C205" t="s">
-        <v>400</v>
+        <v>359</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
@@ -4478,10 +4484,10 @@
         <v>1</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C206" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
@@ -4489,32 +4495,32 @@
         <v>1</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>347</v>
+        <v>387</v>
       </c>
       <c r="C207" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>397</v>
+        <v>343</v>
       </c>
       <c r="C208" t="s">
-        <v>409</v>
+        <v>357</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C209" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -4522,32 +4528,32 @@
         <v>1</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="C210" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>396</v>
+        <v>348</v>
       </c>
       <c r="C211" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="C212" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -4555,10 +4561,10 @@
         <v>1</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C213" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -4566,10 +4572,10 @@
         <v>1</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="C214" t="s">
-        <v>407</v>
+        <v>360</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -4577,10 +4583,10 @@
         <v>1</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C215" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -4588,10 +4594,10 @@
         <v>1</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>66</v>
+        <v>390</v>
       </c>
       <c r="C216" t="s">
-        <v>86</v>
+        <v>402</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -4599,10 +4605,10 @@
         <v>1</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C217" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -4610,10 +4616,10 @@
         <v>1</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C218" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -4621,10 +4627,10 @@
         <v>1</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C219" t="s">
-        <v>554</v>
+        <v>85</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -4632,10 +4638,10 @@
         <v>1</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C220" t="s">
-        <v>88</v>
+        <v>547</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -4643,10 +4649,10 @@
         <v>1</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>555</v>
+        <v>68</v>
       </c>
       <c r="C221" t="s">
-        <v>556</v>
+        <v>88</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -4654,10 +4660,10 @@
         <v>1</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>50</v>
+        <v>548</v>
       </c>
       <c r="C222" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -4665,10 +4671,10 @@
         <v>1</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C223" t="s">
-        <v>90</v>
+        <v>550</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -4676,10 +4682,10 @@
         <v>1</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>558</v>
+        <v>70</v>
       </c>
       <c r="C224" t="s">
-        <v>559</v>
+        <v>90</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -4687,10 +4693,10 @@
         <v>1</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>67</v>
+        <v>551</v>
       </c>
       <c r="C225" t="s">
-        <v>87</v>
+        <v>552</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -4698,10 +4704,10 @@
         <v>1</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C226" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -4709,10 +4715,10 @@
         <v>1</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C227" t="s">
-        <v>560</v>
+        <v>81</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -4720,10 +4726,10 @@
         <v>1</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C228" t="s">
-        <v>79</v>
+        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -4731,10 +4737,10 @@
         <v>1</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C229" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -4742,10 +4748,10 @@
         <v>1</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C230" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -4753,10 +4759,10 @@
         <v>1</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C231" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -4764,10 +4770,10 @@
         <v>1</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C232" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -4775,10 +4781,10 @@
         <v>1</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C233" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -4786,10 +4792,10 @@
         <v>1</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>561</v>
+        <v>53</v>
       </c>
       <c r="C234" t="s">
-        <v>562</v>
+        <v>76</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -4797,10 +4803,10 @@
         <v>1</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>57</v>
+        <v>554</v>
       </c>
       <c r="C235" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -4808,10 +4814,10 @@
         <v>1</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>564</v>
+        <v>57</v>
       </c>
       <c r="C236" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -4819,10 +4825,10 @@
         <v>1</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>64</v>
+        <v>557</v>
       </c>
       <c r="C237" t="s">
-        <v>84</v>
+        <v>558</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -4830,10 +4836,10 @@
         <v>1</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C238" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -4841,10 +4847,10 @@
         <v>1</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C239" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -4852,10 +4858,10 @@
         <v>1</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C240" t="s">
-        <v>566</v>
+        <v>75</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
@@ -4863,10 +4869,10 @@
         <v>1</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C241" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -4874,10 +4880,10 @@
         <v>1</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>568</v>
+        <v>48</v>
       </c>
       <c r="C242" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
@@ -4885,10 +4891,10 @@
         <v>1</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="C243" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
@@ -4896,10 +4902,10 @@
         <v>1</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>49</v>
+        <v>563</v>
       </c>
       <c r="C244" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
@@ -4907,10 +4913,10 @@
         <v>1</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>573</v>
+        <v>49</v>
       </c>
       <c r="C245" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
@@ -4918,10 +4924,10 @@
         <v>1</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>389</v>
+        <v>566</v>
       </c>
       <c r="C246" t="s">
-        <v>402</v>
+        <v>567</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
@@ -4929,10 +4935,10 @@
         <v>1</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C247" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
@@ -4940,10 +4946,10 @@
         <v>1</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C248" t="s">
-        <v>575</v>
+        <v>399</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
@@ -4951,10 +4957,10 @@
         <v>1</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="C249" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
@@ -4962,10 +4968,10 @@
         <v>1</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>283</v>
+        <v>388</v>
       </c>
       <c r="C250" t="s">
-        <v>315</v>
+        <v>569</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
@@ -4973,10 +4979,10 @@
         <v>1</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C251" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
@@ -4984,10 +4990,10 @@
         <v>1</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>577</v>
+        <v>280</v>
       </c>
       <c r="C252" t="s">
-        <v>578</v>
+        <v>312</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -4995,10 +5001,10 @@
         <v>1</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>74</v>
+        <v>570</v>
       </c>
       <c r="C253" t="s">
-        <v>94</v>
+        <v>571</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
@@ -5006,10 +5012,10 @@
         <v>1</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>579</v>
+        <v>74</v>
       </c>
       <c r="C254" t="s">
-        <v>580</v>
+        <v>94</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
@@ -5017,10 +5023,10 @@
         <v>1</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>285</v>
+        <v>572</v>
       </c>
       <c r="C255" t="s">
-        <v>317</v>
+        <v>573</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
@@ -5028,10 +5034,10 @@
         <v>1</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>73</v>
+        <v>281</v>
       </c>
       <c r="C256" t="s">
-        <v>93</v>
+        <v>313</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
@@ -5039,10 +5045,10 @@
         <v>1</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C257" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
@@ -5050,10 +5056,10 @@
         <v>1</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C258" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
@@ -5061,10 +5067,10 @@
         <v>1</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>286</v>
+        <v>71</v>
       </c>
       <c r="C259" t="s">
-        <v>318</v>
+        <v>91</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
@@ -5072,10 +5078,10 @@
         <v>1</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>581</v>
+        <v>282</v>
       </c>
       <c r="C260" t="s">
-        <v>582</v>
+        <v>314</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
@@ -5083,10 +5089,10 @@
         <v>1</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="C261" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.2">
@@ -5094,10 +5100,10 @@
         <v>1</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="C262" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
@@ -5105,21 +5111,21 @@
         <v>1</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>281</v>
+        <v>578</v>
       </c>
       <c r="C263" t="s">
-        <v>313</v>
+        <v>579</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>587</v>
+        <v>277</v>
       </c>
       <c r="C264" t="s">
-        <v>588</v>
+        <v>309</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
@@ -5127,21 +5133,21 @@
         <v>2</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>282</v>
+        <v>580</v>
       </c>
       <c r="C265" t="s">
-        <v>314</v>
+        <v>581</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>589</v>
+        <v>278</v>
       </c>
       <c r="C266" t="s">
-        <v>590</v>
+        <v>310</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
@@ -5149,10 +5155,10 @@
         <v>1</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>280</v>
+        <v>582</v>
       </c>
       <c r="C267" t="s">
-        <v>312</v>
+        <v>583</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
@@ -5160,10 +5166,10 @@
         <v>1</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>591</v>
+        <v>276</v>
       </c>
       <c r="C268" t="s">
-        <v>592</v>
+        <v>308</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
@@ -5171,10 +5177,10 @@
         <v>1</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="C269" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
@@ -5182,10 +5188,10 @@
         <v>1</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>274</v>
+        <v>586</v>
       </c>
       <c r="C270" t="s">
-        <v>306</v>
+        <v>587</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
@@ -5193,10 +5199,10 @@
         <v>1</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C271" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
@@ -5204,10 +5210,10 @@
         <v>1</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C272" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
@@ -5215,10 +5221,10 @@
         <v>1</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>595</v>
+        <v>272</v>
       </c>
       <c r="C273" t="s">
-        <v>596</v>
+        <v>304</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
@@ -5226,10 +5232,10 @@
         <v>1</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>279</v>
+        <v>588</v>
       </c>
       <c r="C274" t="s">
-        <v>311</v>
+        <v>589</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -5237,10 +5243,10 @@
         <v>1</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C275" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
@@ -5248,10 +5254,10 @@
         <v>1</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C276" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
@@ -5259,10 +5265,10 @@
         <v>1</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>597</v>
+        <v>274</v>
       </c>
       <c r="C277" t="s">
-        <v>598</v>
+        <v>306</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
@@ -5270,10 +5276,10 @@
         <v>1</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="C278" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
@@ -5281,43 +5287,43 @@
         <v>1</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>28</v>
+        <v>592</v>
       </c>
       <c r="C279" t="s">
-        <v>39</v>
+        <v>593</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280">
-        <v>2</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C280" s="3" t="s">
-        <v>37</v>
+        <v>1</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C280" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281">
-        <v>1</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C281" t="s">
-        <v>38</v>
+        <v>2</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C282" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
@@ -5325,32 +5331,32 @@
         <v>2</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>601</v>
+        <v>5</v>
       </c>
       <c r="C283" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>29</v>
+        <v>594</v>
       </c>
       <c r="C284" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C285" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -5358,21 +5364,21 @@
         <v>2</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C286" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C287" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
@@ -5380,10 +5386,10 @@
         <v>1</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C288" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
@@ -5391,10 +5397,10 @@
         <v>1</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C289" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
@@ -5402,10 +5408,10 @@
         <v>1</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C290" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
@@ -5413,54 +5419,54 @@
         <v>1</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C291" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C292" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>602</v>
+        <v>35</v>
       </c>
       <c r="C293" t="s">
-        <v>603</v>
+        <v>46</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>2</v>
+        <v>595</v>
       </c>
       <c r="C294" t="s">
-        <v>14</v>
+        <v>596</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C295" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
@@ -5468,10 +5474,10 @@
         <v>1</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C296" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -5479,10 +5485,10 @@
         <v>1</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C297" t="s">
-        <v>412</v>
+        <v>18</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
@@ -5490,75 +5496,86 @@
         <v>1</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>604</v>
+        <v>33</v>
       </c>
       <c r="C298" t="s">
-        <v>605</v>
+        <v>408</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299">
-        <v>10</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C299" s="3" t="s">
-        <v>19</v>
+        <v>1</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C299" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300">
-        <v>1</v>
-      </c>
-      <c r="B300" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C300" t="s">
-        <v>22</v>
+      <c r="B300" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C301" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302">
-        <v>1</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C302" s="3" t="s">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C302" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>1</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C303" t="s">
-        <v>23</v>
+      <c r="B303" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304">
+        <v>1</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C304" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A305">
         <v>2</v>
       </c>
-      <c r="B304" s="1" t="s">
+      <c r="B305" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C304" t="s">
+      <c r="C305" t="s">
         <v>20</v>
       </c>
     </row>
